--- a/IEF_Home/UploadedFiles/3_LT_Vehicles_LIST_Sample_Errors.xlsx
+++ b/IEF_Home/UploadedFiles/3_LT_Vehicles_LIST_Sample_Errors.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20416"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE321CE9-70B2-4FA8-9275-1C8C7A022810}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D96333-893A-4F9E-B5DA-7275861942E6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1140" windowWidth="20418" windowHeight="13440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1140" windowWidth="20418" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -655,10 +655,10 @@
     <t>battery electic bus</t>
   </si>
   <si>
-    <t>wrong label: "battery electic bus" instead of "battery electric bus" (missing r), and label that is defined differently in the classification: "LNG ship" instead of the already defined "ship, LNG".</t>
-  </si>
-  <si>
     <t>ship, liquefied natural gas</t>
+  </si>
+  <si>
+    <t>wrong label: "battery electic bus" instead of "battery electric bus" (missing r), and label that is defined differently in the classification: "ship, liquefied natural gas" instead of the already defined "ship, LNG".</t>
   </si>
 </sst>
 </file>
@@ -2358,7 +2358,7 @@
         <v>29</v>
       </c>
       <c r="F34" s="96" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G34" s="94"/>
       <c r="H34" s="95"/>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="97" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B15" s="37" t="s">
         <v>13</v>
